--- a/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -732,13 +732,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A cinema gives a child ticket to anyone under 13. So a 12-year-old gets one, but a 13-year-old does not. Four coders wrote the age check in different ways, and only one of them still hands a child ticket to a 13-year-old.
-Which condition is the wrong one?</t>
+          <t>A grading chain should label 90 and above as "A", 75-89 as "B", and 60-74 as "C". A developer writes the checks from the lowest boundary upward, and a top scorer of 95 comes out labelled "C":
+```python
+marks = 95
+if marks &gt;= 60:
+    print("C")
+elif marks &gt;= 75:
+    print("B")
+elif marks &gt;= 90:
+    print("A")
+```
+Why does 95 print "C"?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The cut-off is 13: a 12-year-old passes, a 13-year-old fails. `age &lt;= 13` is True at 13, so it wrongly gives the child ticket — that is the broken one. `age &lt; 13` and `age &lt;= 12` both stop at 12, and `age &lt; 13 and age &gt;= 0` is the same rule with a lower floor.</t>
+          <t>An elif chain is checked top to bottom, and the first true condition wins — every branch after it is skipped. For 95, `marks &gt;= 60` is already true, so it prints "C" and never reaches the checks for "B" or "A". The fix is to order the conditions from the highest threshold down.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -776,27 +785,27 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>the-if-statement</t>
+          <t>elif-multi-way-branching</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>age &lt; 13</t>
+          <t>Because 95 is not greater than 90</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>age &lt;= 13</t>
+          <t>Because the first true condition wins — marks &gt;= 60 matches first, so the rest are skipped</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>age &lt; 13 and age &gt;= 0</t>
+          <t>Because an elif chain prints every branch that is true</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>age &lt;= 12</t>
+          <t>Because the else branch is missing</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3" sheetId="1" r:id="Rb417f061462647a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3" sheetId="1" r:id="R62edd5e623334167"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -502,16 +502,16 @@
         <x:v>No ID entered — the text "0" counts as empty</x:v>
       </x:c>
       <x:c r="N2" t="str">
+        <x:v>Tracking parcel — "0" has one character, so it is not empty</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
         <x:v>An error — you cannot put a string after if</x:v>
-      </x:c>
-      <x:c r="O2" t="str">
-        <x:v>Tracking parcel — "0" has one character, so it is not empty</x:v>
       </x:c>
       <x:c r="P2" t="str">
         <x:v>No ID entered — Python turns "0" into the number 0 first</x:v>
       </x:c>
       <x:c r="Q2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
@@ -622,16 +622,16 @@
         <x:v>Because 95 is not greater than 90</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>Because the first true condition wins — marks &gt;= 60 matches first, so the rest are skipped</x:v>
+        <x:v>Because an elif chain prints every branch that is true</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>Because an elif chain prints every branch that is true</x:v>
+        <x:v>Because the else branch is missing</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>Because the else branch is missing</x:v>
+        <x:v>Because the first true condition wins</x:v>
       </x:c>
       <x:c r="Q4" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -681,16 +681,16 @@
         <x:v>&gt; should be !=; it shows No discount</x:v>
       </x:c>
       <x:c r="N5" t="str">
+        <x:v>&gt; should be &gt;=; it shows No discount</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
         <x:v>There is no bug; it shows Discount applied</x:v>
-      </x:c>
-      <x:c r="O5" t="str">
-        <x:v>&gt; should be &gt;=; it shows No discount</x:v>
       </x:c>
       <x:c r="P5" t="str">
         <x:v>&gt; should be ==; it shows Discount applied</x:v>
       </x:c>
       <x:c r="Q5" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -739,19 +739,19 @@
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>Gold — only the top badge shows</x:v>
+        <x:v>Gold</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>Bronze — the first true line stops the rest</x:v>
+        <x:v>Bronze</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>Nothing — the ranges clash</x:v>
+        <x:v>Bronze, Silver, and Gold</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>Bronze, Silver, and Gold — each if runs on its own</x:v>
+        <x:v>Nothing</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -916,13 +916,13 @@
         <x:v>No — Version B skips the soil check</x:v>
       </x:c>
       <x:c r="O9" t="str">
+        <x:v>Yes — both water only when the soil is dry and the tank has water</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
         <x:v>No — Version A checks the tank even when the soil is wet</x:v>
       </x:c>
-      <x:c r="P9" t="str">
-        <x:v>Yes — both water only when the soil is dry and the tank has water</x:v>
-      </x:c>
       <x:c r="Q9" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -930,27 +930,18 @@
         <x:v>Python - MCQ - 3.1.9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>A site accepts a coupon only if it is 8 characters long and not already used. Two coders write the check, then test a 5-character coupon that has never been used:
-```python
-used = False
-code = input("Enter coupon: ")
-# Option 1
-if len(code) != 8:
-    print("Wrong length")
-elif used:
-    print("Already used")
+        <x:v>A signup form intends to reject non-numeric ages before comparing them, but the checks are in an unsafe order:
+```python
+entry = input("Age: ")
+if int(entry) &lt; 18 or not entry.isdigit():
+    print("Invalid age")
 else:
-    print("Coupon applied")
-# Option 2
-if len(code) != 8 and used:
-    print("Invalid coupon")
-else:
-    print("Coupon applied")
-```
-Which version rejects the bad coupon, and why does the other let it through?</x:v>
+    print("Accepted")
+```
+Which input exposes the ordering defect by crashing before the validation message can run?</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>Option 1 checks the two rules one after another, so the wrong length is caught. Option 2 joins them with `and`, so it only rejects a coupon that is BOTH the wrong length AND already used. A 5-character unused coupon fails only one rule, so Option 2 prints `Coupon applied` and lets it through.</x:v>
+        <x:v>With `"x"`, Python tries `int("x")` first and raises `ValueError`; it never reaches `.isdigit()`. Numeric text such as `"17"`, `"25"`, or `"0"` converts successfully. The safe order checks `not entry.isdigit()` before any conversion.</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>10</x:v>
@@ -978,16 +969,16 @@
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>Option 1 rejects it; Option 2 only rejects a coupon that is the wrong length AND already used</x:v>
+        <x:v>`x`</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Both reject it; the two versions behave the same</x:v>
+        <x:v>`17`</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Option 2 rejects it; Option 1 just adds extra branches for no reason</x:v>
+        <x:v>`25`</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>Option 1 rejects it; Option 2 fails because only one of the two checks matters</x:v>
+        <x:v>`0`</x:v>
       </x:c>
       <x:c r="Q10" t="n">
         <x:v>1</x:v>
@@ -1041,13 +1032,13 @@
         <x:v>"Light" if weight &gt; 3000 else "Heavy"</x:v>
       </x:c>
       <x:c r="O11" t="str">
+        <x:v>"Heavy" if weight &gt; 3000</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
         <x:v>"Heavy" if weight &gt; 3000 else "Light"</x:v>
       </x:c>
-      <x:c r="P11" t="str">
-        <x:v>"Heavy" if weight &gt; 3000</x:v>
-      </x:c>
       <x:c r="Q11" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1055,15 +1046,18 @@
         <x:v>Python - MCQ - 3.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>A ward monitor should alert when the temperature reaches 38.0°C. A tester wants the single reading that would reveal the bug if someone wrote `&gt;` instead of `&gt;=`:
-```python
-def needs_alert(temp):
-    return temp &gt;= 38.0
-```
-Which reading must be in the test?</x:v>
+        <x:v>A ward monitor should alert when the temperature reaches 38.0°C, but its comparison excludes the exact boundary:
+```python
+temp = 38.0
+if temp &gt; 38.0:
+    print("Alert")
+else:
+    print("Normal")
+```
+Which test reading exposes the boundary defect?</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>`&gt;=` and `&gt;` give different answers only at the exact number. `needs_alert(38.0)` is True with `&gt;=`, but would be False with `&gt;`. Any reading away from 38.0 gives the same answer either way, so only 38.0 catches the mistake.</x:v>
+        <x:v>The incorrect `&gt;` and the required `&gt;=` differ only at exactly 38.0. At that reading, the current code prints `Normal`, while the rule requires `Alert`. Values above or below the boundary do not distinguish the two operators.</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>8</x:v>
@@ -1172,15 +1166,18 @@
         <x:v>Python - MCQ - 3.2.3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>During testing, this age check is always called with whole numbers, and every call passes. But in the real app the value comes straight from `input()`:
-```python
-def check_can_vote(age):
-    return "Eligible" if age &gt;= 18 else "Not eligible"
-```
-Which single call behaves like the real app and reveals the hidden problem?</x:v>
+        <x:v>An age arrives directly from `input()`, so it is text when the comparison runs:
+```python
+age = input("Age: ")
+if age &gt;= 18:
+    print("Eligible")
+else:
+    print("Not eligible")
+```
+Which is the smallest correct repair?</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>`input()` always returns a string, so the real app passes text like `"25"`. Comparing `"25" &gt;= 18` compares a string to a number, which raises a `TypeError` in Python 3. Calls with plain numbers — normal or extreme — never hit this, which is why the tests missed it.</x:v>
+        <x:v>`input()` returns text, and text cannot be ordered against the integer 18. Converting at the point of input with `age = int(input("Age: "))` makes both sides numeric before the comparison. Comparing with the text `"18"` would use character ordering rather than numeric age ordering.</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>8</x:v>
@@ -1208,19 +1205,19 @@
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>check_can_vote("25")</x:v>
+        <x:v>Use `age = str(input("Age: "))`</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>check_can_vote(25)</x:v>
+        <x:v>Use `age = input("Age: ") + 0`</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>check_can_vote(16)</x:v>
+        <x:v>Use `age = int(input("Age: "))`</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>check_can_vote(0)</x:v>
+        <x:v>Change the test to `age &gt;= "18"`</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1270,16 +1267,16 @@
         <x:v>It should be &gt;= 14 to include the 14th day</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Nothing is wrong — 20 days is within the limit</x:v>
+        <x:v>&lt; should be &gt;</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>&lt; should be &gt; — the fee is for more than 14 days, not fewer</x:v>
+        <x:v>Nothing is wrong</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>The else branch should print the fee</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1329,7 +1326,7 @@
         <x:v>The comparisons are backwards</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>and should be or — no number is below -50 and above 150 at once</x:v>
+        <x:v>and should be or</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>The else needs its own condition</x:v>
@@ -1513,13 +1510,13 @@
         <x:v>active and checked_in</x:v>
       </x:c>
       <x:c r="O19" t="str">
+        <x:v>not active and not checked_in</x:v>
+      </x:c>
+      <x:c r="P19" t="str">
         <x:v>active and not checked_in</x:v>
       </x:c>
-      <x:c r="P19" t="str">
-        <x:v>not active and not checked_in</x:v>
-      </x:c>
       <x:c r="Q19" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1568,10 +1565,10 @@
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20" t="str">
+        <x:v>Version A stores "Approved", Version B stores "Rejected"</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
         <x:v>Both store "Approved"</x:v>
-      </x:c>
-      <x:c r="N20" t="str">
-        <x:v>Version A stores "Approved", Version B stores "Rejected"</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Both store "Rejected"</x:v>
@@ -1580,7 +1577,7 @@
         <x:v>Version A stores "Rejected", Version B stores "Approved"</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1650,11 +1647,10 @@
         <x:v>Python - MCQ - 3.2.11</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>A dashboard shows one label per rating: under 3 is "Improve", 3 to 4 is "Meets", over 4 is "Exceeds". It must never show two labels, and never show none.
-Which structure guarantees exactly one label for any rating?</x:v>
+        <x:v>A dashboard has mutually exclusive rating bands and needs a clear fallback for any value not covered explicitly. Which structure communicates that design most directly?</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>An `if`-`elif`-`else` chain runs only the first matching branch, and the `else` covers everything left over — so exactly one label always shows. Separate `if`s could fire more than once, one `if` with `or` cannot pick a different label per range, and `match-case` is for fixed values, not ranges.</x:v>
+        <x:v>An `if`-`elif`-`else` chain makes the mutual exclusivity explicit: the first matching band runs and the final `else` provides a fallback. Carefully written separate `if` statements could also be mutually exclusive, but the chain expresses the intended one-path design more clearly and is safer to maintain.</x:v>
       </x:c>
       <x:c r="D22" t="n">
         <x:v>8</x:v>
@@ -1682,16 +1678,16 @@
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>An if-elif-else chain</x:v>
+        <x:v>An `if`-`elif`-`else` chain</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Three separate if statements</x:v>
+        <x:v>Three unrelated `if` statements</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>One if with the ranges joined by or</x:v>
+        <x:v>One `if` joining every band with `or`</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>A match-case that compares the rating to each number</x:v>
+        <x:v>A `match` comparing every possible rating</x:v>
       </x:c>
       <x:c r="Q22" t="n">
         <x:v>1</x:v>
@@ -1744,19 +1740,19 @@
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
+        <x:v>The order is wrong</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
         <x:v>The else should say gb &gt; 10</x:v>
       </x:c>
-      <x:c r="N23" t="str">
+      <x:c r="O23" t="str">
         <x:v>Every &lt;= should be &lt;</x:v>
-      </x:c>
-      <x:c r="O23" t="str">
-        <x:v>The order is wrong — gb &lt;= 10 catches small usage first</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>The free and top tiers need a lower bound with and</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1808,16 +1804,16 @@
         <x:v>Invalid card</x:v>
       </x:c>
       <x:c r="N24" t="str">
+        <x:v>Unlocked</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
         <x:v>Nothing</x:v>
-      </x:c>
-      <x:c r="O24" t="str">
-        <x:v>Unlocked</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>Both Unlocked and Invalid card</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1872,16 +1868,16 @@
         <x:v>English selected — match ignores capitals</x:v>
       </x:c>
       <x:c r="N25" t="str">
+        <x:v>Language not supported — "EN" does not equal "en", so no case matches</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
         <x:v>Nothing — match errors when no case matches</x:v>
       </x:c>
-      <x:c r="O25" t="str">
+      <x:c r="P25" t="str">
         <x:v>English selected — the _ case jumps to the first case</x:v>
       </x:c>
-      <x:c r="P25" t="str">
-        <x:v>Language not supported — "EN" does not equal "en", so no case matches</x:v>
-      </x:c>
       <x:c r="Q25" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1928,10 +1924,10 @@
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
+        <x:v>Subject required — a string of only spaces counts as empty</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
         <x:v>Ticket created — spaces still count as characters, so the string is not empty</x:v>
-      </x:c>
-      <x:c r="N26" t="str">
-        <x:v>Subject required — a string of only spaces counts as empty</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>An error — spaces cannot be tested in an if</x:v>
@@ -1940,7 +1936,7 @@
         <x:v>Subject required — Python removes the spaces first</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1996,16 +1992,16 @@
         <x:v>Robot idle</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>Order queued — waiting for a slot</x:v>
+        <x:v>Idle move to zone</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Idle move to zone</x:v>
+        <x:v>Order queued</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>Robot dispatched</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2113,16 +2109,16 @@
         <x:v>systolic &gt; 90 and systolic &lt; 120</x:v>
       </x:c>
       <x:c r="N29" t="str">
+        <x:v>90 &lt;= systolic &lt;= 120</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
         <x:v>systolic &gt;= 90 or systolic &lt;= 120</x:v>
       </x:c>
-      <x:c r="O29" t="str">
+      <x:c r="P29" t="str">
         <x:v>systolic == 90 and systolic == 120</x:v>
       </x:c>
-      <x:c r="P29" t="str">
-        <x:v>90 &lt;= systolic &lt;= 120</x:v>
-      </x:c>
       <x:c r="Q29" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2171,19 +2167,19 @@
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>The second branch — it repeats the first condition; the customer sees Free next-day delivery</x:v>
+        <x:v>The else</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>The else — the customer sees Free standard delivery</x:v>
+        <x:v>The if and the elif both</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>The if and the elif both — everyone sees Paid delivery</x:v>
+        <x:v>The second branch</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>None — all three run and two lines print</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2231,16 +2227,16 @@
         <x:v>"Qualified" if score &gt; 60 else "Try again"</x:v>
       </x:c>
       <x:c r="N31" t="str">
+        <x:v>if score &gt;= 60: "Qualified" else: "Try again"</x:v>
+      </x:c>
+      <x:c r="O31" t="str">
+        <x:v>"Try again" if score &gt;= 60 else "Qualified"</x:v>
+      </x:c>
+      <x:c r="P31" t="str">
         <x:v>"Qualified" if score &gt;= 60 else "Try again"</x:v>
       </x:c>
-      <x:c r="O31" t="str">
-        <x:v>if score &gt;= 60: "Qualified" else: "Try again"</x:v>
-      </x:c>
-      <x:c r="P31" t="str">
-        <x:v>"Try again" if score &gt;= 60 else "Qualified"</x:v>
-      </x:c>
       <x:c r="Q31" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2285,19 +2281,19 @@
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
+        <x:v>stock &lt; 20</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
         <x:v>stock &lt;= 20</x:v>
       </x:c>
-      <x:c r="N32" t="str">
+      <x:c r="O32" t="str">
         <x:v>stock &gt; 20</x:v>
-      </x:c>
-      <x:c r="O32" t="str">
-        <x:v>stock &lt; 20</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>stock == 20</x:v>
       </x:c>
       <x:c r="Q32" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2355,13 +2351,13 @@
         <x:v>Yes — they differ at temp == 17</x:v>
       </x:c>
       <x:c r="O33" t="str">
+        <x:v>No — one of the two opposite conditions is always true, so both set the same value</x:v>
+      </x:c>
+      <x:c r="P33" t="str">
         <x:v>Yes — two ifs always set the value twice</x:v>
       </x:c>
-      <x:c r="P33" t="str">
-        <x:v>No — one of the two opposite conditions is always true, so both set the same value</x:v>
-      </x:c>
       <x:c r="Q33" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2414,19 +2410,19 @@
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
+        <x:v>Yes — they always match</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>No — Version A flags small foreign payments</x:v>
+      </x:c>
+      <x:c r="O34" t="str">
         <x:v>No — Version A prints nothing, but Version B prints Domestic large payment</x:v>
-      </x:c>
-      <x:c r="N34" t="str">
-        <x:v>Yes — they always match</x:v>
-      </x:c>
-      <x:c r="O34" t="str">
-        <x:v>No — Version A flags small foreign payments</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>No — Version B never checks foreign</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2482,16 +2478,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N35" t="str">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O35" t="str">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="P35" t="str">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="O35" t="str">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="P35" t="str">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="Q35" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2538,19 +2534,19 @@
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>Prints Processing 50 — isdigit ignores the letter</x:v>
+        <x:v>Prints Processing 50</x:v>
       </x:c>
       <x:c r="N36" t="str">
         <x:v>Crashes on int() with an error</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Prints Enter numbers only — "50x" is not all digits</x:v>
+        <x:v>Prints Processing 50x</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Prints Processing 50x</x:v>
+        <x:v>Prints Enter numbers only</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2600,19 +2596,19 @@
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>Nothing stops it — Upload accepted</x:v>
+        <x:v>Nothing stops it</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>The name check stops it — File name required</x:v>
+        <x:v>The name check stops it</x:v>
       </x:c>
       <x:c r="O37" t="str">
+        <x:v>The size check stops it</x:v>
+      </x:c>
+      <x:c r="P37" t="str">
         <x:v>It crashes comparing size to 5</x:v>
       </x:c>
-      <x:c r="P37" t="str">
-        <x:v>The size check stops it — File too large</x:v>
-      </x:c>
       <x:c r="Q37" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2661,10 +2657,10 @@
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
+        <x:v>Menu closed only</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
         <x:v>Balance, then Menu closed</x:v>
-      </x:c>
-      <x:c r="N38" t="str">
-        <x:v>Menu closed only</x:v>
       </x:c>
       <x:c r="O38" t="str">
         <x:v>An error because case _ is required</x:v>
@@ -2673,7 +2669,7 @@
         <x:v>Nothing</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2794,14 +2790,14 @@
 `else: print("Must be 18 or older")`</x:v>
       </x:c>
       <x:c r="N40" t="str">
+        <x:v>`if not entry.isdigit(): print("Digits only")`
+`elif int(entry) &lt; 18: print("Must be 18 or older")`
+`else: print("Accepted")`</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
         <x:v>`if entry.isdigit(): print("Accepted")`
 `elif int(entry) &lt; 18: print("Must be 18 or older")`
 `else: print("Digits only")`</x:v>
-      </x:c>
-      <x:c r="O40" t="str">
-        <x:v>`if not entry.isdigit(): print("Digits only")`
-`elif int(entry) &lt; 18: print("Must be 18 or older")`
-`else: print("Accepted")`</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>`if not entry.isdigit(): print("Digits only")`
@@ -2809,7 +2805,7 @@
 `else: print("Accepted")`</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="41">

--- a/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 3 - Control Flow/Unit 3 - Control Flow - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3" sheetId="1" r:id="R62edd5e623334167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 3" sheetId="1" r:id="R26a7b33252ea48b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -455,23 +455,24 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+    <x:row r="2" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A2" t="str">
         <x:v>Python - MCQ - 3.1.1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>A tracking page starts a lookup only if the customer typed an ID. Here the ID is the text "0":
+        <x:v>A laboratory technician is configuring a vaccine-storage alert that must accept only the approved temperature interval.
+A medicine is safe only from 2°C through 8°C, including both endpoints:
 ```python
-tracking_id = "0"
-if tracking_id:
-    print("Tracking parcel")
+temperature = 8
+if __________:
+    action = "Store"
 else:
-    print("No ID entered")
+    action = "Reject"
 ```
-A teammate says the lookup will be skipped, because "0 means empty". What does the code print?</x:v>
+Select the expression that completes the gate without admitting any outside temperature.</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>The value is the text `"0"`, which has one character, so it is not an empty string. A non-empty string is truthy, so the `if` runs and prints `Tracking parcel`. Only the number `0` is falsy, not the text `"0"` — so the teammate is wrong.</x:v>
+        <x:v>The chained comparison requires both inclusive limits to hold, so 2 and 8 are accepted and outside values are rejected.</x:v>
       </x:c>
       <x:c r="D2" t="n">
         <x:v>8</x:v>
@@ -483,7 +484,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G2" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H2" t="str">
         <x:v>python - Set 1</x:v>
@@ -495,42 +496,35 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L2"/>
       <x:c r="M2" t="str">
-        <x:v>No ID entered — the text "0" counts as empty</x:v>
+        <x:v>`temperature &gt; 2 or temperature &lt; 8`</x:v>
       </x:c>
       <x:c r="N2" t="str">
-        <x:v>Tracking parcel — "0" has one character, so it is not empty</x:v>
+        <x:v>`temperature &gt;= 2 or temperature &lt;= 8`</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>An error — you cannot put a string after if</x:v>
+        <x:v>`2 &lt;= temperature &lt;= 8`</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>No ID entered — Python turns "0" into the number 0 first</x:v>
+        <x:v>`temperature &gt; 2 and temperature &lt; 8`</x:v>
       </x:c>
       <x:c r="Q2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="18" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A3" t="str">
         <x:v>Python - MCQ - 3.1.2</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>An online store gives free shipping once a cart goes past ₹999. So a cart of ₹999 must still pay for shipping, but a cart of ₹1000 gets it free. The cart below is exactly ₹999:
-```python
-cart_total = 999
-if ________:
-    print("Free shipping unlocked")
-else:
-    print("Pay for shipping")
-```
-Which condition gives the right result for this ₹999 cart?</x:v>
+        <x:v>An HR portal needs a compact age-group assignment that another developer can read and run without modification.
+The requirement is to store `"Adult"` for ages 18 and above and `"Minor"` otherwise. Choose the line that both compiles and implements the rule.</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>A ₹999 cart must NOT get free shipping. `cart_total &gt; 999` is `999 &gt; 999` → False, so it correctly prints `Pay for shipping`, and a ₹1000 cart would pass. `&gt;= 999` would wrongly free the ₹999 cart, `&lt; 999` reverses the rule, and `== 999` matches only that one value.</x:v>
+        <x:v>Python's conditional-expression order is `value_if_true if condition else value_if_false`.</x:v>
       </x:c>
       <x:c r="D3" t="n">
         <x:v>5</x:v>
@@ -542,7 +536,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>apply</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H3" t="str">
         <x:v>python - Set 1</x:v>
@@ -554,44 +548,43 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>the-if-statement</x:v>
+        <x:v>conditional-expressions</x:v>
       </x:c>
       <x:c r="L3"/>
       <x:c r="M3" t="str">
-        <x:v>cart_total &gt; 999</x:v>
+        <x:v>`group = "Adult" if age &gt;= 18 else "Minor"`</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>cart_total &gt;= 999</x:v>
+        <x:v>`group = if age &gt;= 18 "Adult" else "Minor"`</x:v>
       </x:c>
       <x:c r="O3" t="str">
-        <x:v>cart_total &lt; 999</x:v>
+        <x:v>`group = "Adult" when age &gt;= 18 otherwise "Minor"`</x:v>
       </x:c>
       <x:c r="P3" t="str">
-        <x:v>cart_total == 999</x:v>
+        <x:v>`group = age &gt;= 18 ? "Adult" : "Minor"`</x:v>
       </x:c>
       <x:c r="Q3" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 3.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A grading chain should label 90 and above as "A", 75-89 as "B", and 60-74 as "C". A developer writes the checks from the lowest boundary upward, and a top scorer of 95 comes out labelled "C":
+        <x:v>A command-line tool fails during deployment before operators can issue even the first supported command.
 ```python
-marks = 95
-if marks &gt;= 60:
-    print("C")
-elif marks &gt;= 75:
-    print("B")
-elif marks &gt;= 90:
-    print("A")
+command = "stop"
+match command:
+    case _:
+        message = "Unknown"
+    case "stop":
+        message = "Stopping"
 ```
-Why does 95 print "C"?</x:v>
+Record the correct build outcome.</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>An elif chain is checked top to bottom, and the first true condition wins — every branch after it is skipped. For 95, `marks &gt;= 60` is already true, so it prints "C" and never reaches the checks for "B" or "A". The fix is to order the conditions from the highest threshold down.</x:v>
+        <x:v>`case _` matches every value. Python does not permit a later case that can never be reached.</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>8</x:v>
@@ -603,7 +596,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>python - Set 1</x:v>
@@ -615,54 +608,51 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>elif-multi-way-branching</x:v>
+        <x:v>match-case</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>Because 95 is not greater than 90</x:v>
+        <x:v>`message` becomes `"Unknown"`.</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>Because an elif chain prints every branch that is true</x:v>
+        <x:v>`message` becomes `"Stopping"`.</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>Because the else branch is missing</x:v>
+        <x:v>Both case bodies execute.</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>Because the first true condition wins</x:v>
+        <x:v>Python reports a syntax error because a wildcard makes the later case unreachable.</x:v>
       </x:c>
       <x:c r="Q4" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 3.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A shop gives a discount on any bill of ₹2000 or more. But customers billed exactly ₹2000 keep complaining that they never get it:
+        <x:v>A venue team is auditing an access rule after a blocked VIP was unexpectedly admitted.
+The deployed rule is:
 ```python
-bill = 2000
-if bill &gt; 2000:
-    print("Discount applied")
-else:
-    print("No discount")
+allowed = not blocked and has_ticket or is_vip
 ```
-What is the bug, and what shows for a ₹2000 bill?</x:v>
+For `blocked = True`, `has_ticket = False`, and `is_vip = True`, which truth-table row is correct?</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>"₹2000 or more" must include 2000, so the test needs `&gt;=`. With `&gt;`, a bill of exactly 2000 fails and the `else` runs, showing `No discount` — the exact complaint. Changing `&gt;` to `&gt;=` fixes it.</x:v>
+        <x:v>The expression groups as `((not blocked) and has_ticket) or is_vip`; VIP status makes the final result true.</x:v>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>python - Set 1</x:v>
@@ -674,56 +664,58 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>if-else</x:v>
+        <x:v>truthiness-and-boolean-logic</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5" t="str">
-        <x:v>&gt; should be !=; it shows No discount</x:v>
+        <x:v>`not blocked = True`, `allowed = False`</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>&gt; should be &gt;=; it shows No discount</x:v>
+        <x:v>`not blocked = False`, `allowed = True`</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>There is no bug; it shows Discount applied</x:v>
+        <x:v>`not blocked = False`, `allowed = False`</x:v>
       </x:c>
       <x:c r="P5" t="str">
-        <x:v>&gt; should be ==; it shows Discount applied</x:v>
+        <x:v>`not blocked = True`, `allowed = True`</x:v>
       </x:c>
       <x:c r="Q5" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Python - MCQ - 3.1.5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>A fitness band should give one badge per day. But users with high step counts say several badges pop up at once. Here is the badge code for a 12,000-step day:
+        <x:v>A cinema kiosk must distinguish a minor with a ticket from a visitor who has no ticket at all.
 ```python
-steps = 12000
-if steps &gt;= 5000:
-    print("Bronze")
-if steps &gt;= 8000:
-    print("Silver")
-if steps &gt;= 10000:
-    print("Gold")
+has_ticket = True
+age = 15
+if has_ticket:
+    if age &gt;= 18:
+        instruction = "Enter alone"
+    else:
+        instruction = "Adult required"
+else:
+    instruction = "Buy ticket"
 ```
-What does it print, and why do users see a pile-up?</x:v>
+Complete the trace statement: “The first `else` pairs with _____, therefore `instruction` becomes _____.”</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>These are three separate `if` statements, not one `elif` chain. At 12,000 steps every condition is True, so all three run and print `Bronze`, `Silver`, and `Gold` — the pile-up. Using `elif` for the last two would let only one badge show.</x:v>
+        <x:v>Indentation pairs the first `else` with the inner age check. The ticket check passes, but the age check does not.</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>analyze</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H6" t="str">
         <x:v>python - Set 1</x:v>
@@ -735,35 +727,43 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>if-else</x:v>
+        <x:v>nested-conditions</x:v>
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>Gold</x:v>
+        <x:v>`if has_ticket`; `"Buy ticket"`</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>Bronze</x:v>
+        <x:v>`if age &gt;= 18`; `"Adult required"`</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>Bronze, Silver, and Gold</x:v>
+        <x:v>`if has_ticket`; `"Adult required"`</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>Nothing</x:v>
+        <x:v>`if age &gt;= 18`; `"Buy ticket"`</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>Python - MCQ - 3.1.6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>An app must turn one typed word — "lights", "fan", "tv", or "ac" — into an action, and reply "Not recognised" for anything else. Every choice compares the same word against a fixed value.
-Which structure fits this best?</x:v>
+        <x:v>A registration kiosk sometimes crashes before it can show its intended validation message.
+```python
+raw_age = input("Age: ")
+age = int(raw_age)
+if raw_age.isdigit() and 1 &lt;= age &lt;= 120:
+    result = "Accepted"
+else:
+    result = "Rejected"
+```
+QA wants a test that proves validation occurs too late. Which input provides the clearest evidence?</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Comparing one value to several fixed options, with a default for the rest, is exactly what `match-case` is for — `case _` handles anything unknown. Four equality-based `if` statements would repeat the same comparison and need extra logic for an unknown word; they would not all match the same word. One `if` with `or` cannot choose a different action per word, and deep nesting only adds clutter.</x:v>
+        <x:v>`int("abc")` raises `ValueError` before `.isdigit()` is checked, demonstrating that text must be validated before conversion.</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>8</x:v>
@@ -775,7 +775,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>python - Set 1</x:v>
@@ -787,41 +787,43 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>match-case</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7" t="str">
-        <x:v>A match-case block with a case _ for anything else</x:v>
+        <x:v>`"1"`</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Four separate if statements, one per word</x:v>
+        <x:v>`"120"`</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>One if that joins all four words with or</x:v>
+        <x:v>`"121"`</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>An if-else nested four levels deep</x:v>
+        <x:v>`"abc"`</x:v>
       </x:c>
       <x:c r="Q7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>Python - MCQ - 3.1.7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>An insurer approves a claim only if the policy is active AND the claim is "medical" or "accident". A coder thinks all four lines below mean the same thing. To settle it, they test an inactive policy with an "accident" claim — which must be rejected:
+        <x:v>A grading portal never awards distinction even when students clearly cross the highest threshold.
 ```python
-active = False
-claim_type = "accident"
-if ________:
-    print("Claim approved")
+if score &gt;= 40:
+    result = "Pass"
+elif score &gt;= 80:
+    result = "Distinction"
+else:
+    result = "Fail"
 ```
-Which condition correctly rejects this claim?</x:v>
+The labels and thresholds are correct; only their order may change. Approve the smallest valid repair.</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>`and` is checked before `or`. Line A reads as `(active and medical) or accident` → `(False and ...) or True` → True, so it wrongly approves. Line B puts brackets around the two claim types: `False and (False or True)` → `False and True` → False, so it rejects — correct. Line C's leading `or` drops the active rule, and line D needs both claim types at once, which is impossible.</x:v>
+        <x:v>Values at least 80 already satisfy `&gt;= 40`. Testing the narrower, higher threshold first makes both branches reachable.</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>10</x:v>
@@ -845,411 +847,410 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8" t="str">
-        <x:v>active and claim_type == "medical" or claim_type == "accident"</x:v>
+        <x:v>Test `score &gt;= 80` first, then `score &gt;= 40`.</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>active and (claim_type == "medical" or claim_type == "accident")</x:v>
+        <x:v>Replace `elif` with a second independent `if`.</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>active or claim_type == "medical" and claim_type == "accident"</x:v>
+        <x:v>Move `else` between the two comparisons.</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>active and claim_type == "medical" and claim_type == "accident"</x:v>
+        <x:v>Reverse the labels while leaving the conditions in place.</x:v>
       </x:c>
       <x:c r="Q8" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>Python - MCQ - 3.1.8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>A garden system waters a bed only when the soil is dry AND the tank has water. Two coders write it differently. Notice the inner `if` has no `else`:
+        <x:v>A form engine uses Python truthiness to decide whether submitted values contain meaningful data.
+Select the row in which both values on the left are falsy and both values on the right are truthy.</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Numeric zero and empty text are falsy. Non-empty text and a non-empty list are truthy even when they contain a zero-like value.</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>understand</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>truthiness-and-boolean-logic</x:v>
+      </x:c>
+      <x:c r="L9"/>
+      <x:c r="M9" t="str">
+        <x:v>Falsy: `"0"`, `[0]`; Truthy: `0`, `[]`</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>Falsy: `" "`, `1`; Truthy: `""`, `None`</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>Falsy: `0`, `""`; Truthy: `"0"`, `[0]`</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>Falsy: `False`, `"False"`; Truthy: `{}`, `0.0`</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Python - MCQ - 3.1.9</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>An exam-entry form must reject malformed marks without crashing or accepting an impossible score.
+A mark must contain digits and lie from 0 through 100. Choose the implementation that never calls `int()` on invalid text and distinguishes malformed input from an out-of-range number.</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>The text check guards the conversion. Only digit-only input is converted, after which the inclusive range is evaluated.</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>input-validation</x:v>
+      </x:c>
+      <x:c r="L10"/>
+      <x:c r="M10" t="str">
+        <x:v>```python
+mark = int(raw)
+if 0 &lt;= mark &lt;= 100:
+    result = "Accepted"
+```</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>```python
+if raw:
+    result = "Accepted"
+else:
+    result = "Rejected"
+```</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>```python
+if not raw.isdigit() and int(raw) &gt; 100:
+    result = "Rejected"
+else:
+    result = "Accepted"
+```</x:v>
+      </x:c>
+      <x:c r="P10" t="str">
+        <x:v>```python
+if not raw.isdigit():
+    result = "Digits required"
+else:
+    mark = int(raw)
+    result = "Accepted" if 0 &lt;= mark &lt;= 100 else "Out of range"
+```</x:v>
+      </x:c>
+      <x:c r="Q10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>Python - MCQ - 3.1.10</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>A streaming portal must verify sign-in before it examines a customer's subscription.
+The portal should require sign-in before checking whether a subscription is active:
+```python
+if signed_in:
+    __________
+        access = "Play"
+    else:
+        access = "Renew"
+else:
+    access = "Sign in"
+```
+Choose the missing line, including its indentation and punctuation.</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>A nested `if` must be indented inside the signed-in branch and end with a colon.</x:v>
+      </x:c>
+      <x:c r="D11" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>nested-conditions</x:v>
+      </x:c>
+      <x:c r="L11"/>
+      <x:c r="M11" t="str">
+        <x:v>`else subscription_active:`</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>`if subscription_active:`</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>`match subscription_active`</x:v>
+      </x:c>
+      <x:c r="P11" t="str">
+        <x:v>`subscription_active == True`</x:v>
+      </x:c>
+      <x:c r="Q11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>Python - MCQ - 3.2.1</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>A transit-wallet service applies a purchase and then a low-balance adjustment during the same transaction.
+```python
+wallet = 900
+cost = 650
+if cost &lt;= wallet:
+    wallet -= cost
+if wallet &lt; 300:
+    wallet += 50
+```
+Enter the value that remains in `wallet` after both decisions.</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>The purchase reduces the wallet to 250; the low-balance condition then adds 50, leaving 300.</x:v>
+      </x:c>
+      <x:c r="D12" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>conditional-statements</x:v>
+      </x:c>
+      <x:c r="L12"/>
+      <x:c r="M12" t="str">
+        <x:v>`300`</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>`250`</x:v>
+      </x:c>
+      <x:c r="O12" t="str">
+        <x:v>`950`</x:v>
+      </x:c>
+      <x:c r="P12" t="str">
+        <x:v>`200`</x:v>
+      </x:c>
+      <x:c r="Q12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Python - MCQ - 3.2.2</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>A registration policy has an age boundary, and QA wants the most informative single test.
+The policy says “18 or older,” but the implementation is `if age &gt; 18:`. QA has time for one test.</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Eighteen is the inclusive boundary promised by the policy and the exact value incorrectly rejected by `&gt;`.</x:v>
+      </x:c>
+      <x:c r="D13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>input-validation</x:v>
+      </x:c>
+      <x:c r="L13"/>
+      <x:c r="M13" t="str">
+        <x:v>`0`</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>`17`</x:v>
+      </x:c>
+      <x:c r="O13" t="str">
+        <x:v>`18`</x:v>
+      </x:c>
+      <x:c r="P13" t="str">
+        <x:v>`19`</x:v>
+      </x:c>
+      <x:c r="Q13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Python - MCQ - 3.2.3</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>A banking team wants to correct an access policy with the least disruptive code change.
+Access requires both a correct PIN and an active account:
+```python
+if pin_correct or account_active:
+    access = "Granted"
+else:
+    access = "Denied"
+```
+Select the one-token replacement.</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Both facts are mandatory, so conjunction rather than disjunction represents the policy.</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>truthiness-and-boolean-logic</x:v>
+      </x:c>
+      <x:c r="L14"/>
+      <x:c r="M14" t="str">
+        <x:v>Replace `if` with `elif`.</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>Replace `or` with `and`.</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>Replace `else` with `match`.</x:v>
+      </x:c>
+      <x:c r="P14" t="str">
+        <x:v>Replace `active_account` with `not active_account`.</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="132" hidden="0" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>Python - MCQ - 3.2.4</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>A security engineer is simplifying login-rejection logic and must preserve every Boolean outcome.
 ```python
 # Version A
-if soil_dry:
-    if tank_has_water:
-        print("Watering")
-# Version B
-if soil_dry and tank_has_water:
-    print("Watering")
+reject = not (pin_correct and account_active)
+# Version B candidates
 ```
-Do the two versions always behave the same?</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>A nested `if` with no inner `else` is the same as one `if` joined by `and`: both water only when soil is dry and the tank has water, and both do nothing otherwise. So they always match; Version B is just easier to read.</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>nested-conditions-and-guard-clauses</x:v>
-      </x:c>
-      <x:c r="L9"/>
-      <x:c r="M9" t="str">
-        <x:v>No — Version A also waters when the tank is empty</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
-        <x:v>No — Version B skips the soil check</x:v>
-      </x:c>
-      <x:c r="O9" t="str">
-        <x:v>Yes — both water only when the soil is dry and the tank has water</x:v>
-      </x:c>
-      <x:c r="P9" t="str">
-        <x:v>No — Version A checks the tank even when the soil is wet</x:v>
-      </x:c>
-      <x:c r="Q9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Python - MCQ - 3.1.9</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>A signup form intends to reject non-numeric ages before comparing them, but the checks are in an unsafe order:
-```python
-entry = input("Age: ")
-if int(entry) &lt; 18 or not entry.isdigit():
-    print("Invalid age")
-else:
-    print("Accepted")
-```
-Which input exposes the ordering defect by crashing before the validation message can run?</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>With `"x"`, Python tries `int("x")` first and raises `ValueError`; it never reaches `.isdigit()`. Numeric text such as `"17"`, `"25"`, or `"0"` converts successfully. The safe order checks `not entry.isdigit()` before any conversion.</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
+Which candidate produces the same `reject` value for all four Boolean combinations?</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>By De Morgan's law, negating `A and B` produces `not A or not B`.</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E10" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
+      <x:c r="E15" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
         <x:v>hard</x:v>
       </x:c>
-      <x:c r="G10" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I10" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>input-validation</x:v>
-      </x:c>
-      <x:c r="L10"/>
-      <x:c r="M10" t="str">
-        <x:v>`x`</x:v>
-      </x:c>
-      <x:c r="N10" t="str">
-        <x:v>`17`</x:v>
-      </x:c>
-      <x:c r="O10" t="str">
-        <x:v>`25`</x:v>
-      </x:c>
-      <x:c r="P10" t="str">
-        <x:v>`0`</x:v>
-      </x:c>
-      <x:c r="Q10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Python - MCQ - 3.1.10</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>A toll booth needs a one-line label: "Heavy" above 3000 kg, otherwise "Light". Three of the four lines below are broken — one uses statement syntax, one swaps the labels, one is missing a part:
-```python
-weight = 2500
-category = ________
-print(category)
-```
-Which line is the correct one?</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>A conditional expression is written `value_if_true if condition else value_if_false`, so `"Heavy" if weight &gt; 3000 else "Light"` is right. Line A is `if`/`else` statement syntax, not an expression; line B swaps the two labels; line D is missing the `else` part.</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="G11" t="str">
+      <x:c r="G15" t="str">
         <x:v>apply</x:v>
       </x:c>
-      <x:c r="H11" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>conditional-ternary-expressions</x:v>
-      </x:c>
-      <x:c r="L11"/>
-      <x:c r="M11" t="str">
-        <x:v>if weight &gt; 3000: "Heavy" else: "Light"</x:v>
-      </x:c>
-      <x:c r="N11" t="str">
-        <x:v>"Light" if weight &gt; 3000 else "Heavy"</x:v>
-      </x:c>
-      <x:c r="O11" t="str">
-        <x:v>"Heavy" if weight &gt; 3000</x:v>
-      </x:c>
-      <x:c r="P11" t="str">
-        <x:v>"Heavy" if weight &gt; 3000 else "Light"</x:v>
-      </x:c>
-      <x:c r="Q11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Python - MCQ - 3.2.1</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>A ward monitor should alert when the temperature reaches 38.0°C, but its comparison excludes the exact boundary:
-```python
-temp = 38.0
-if temp &gt; 38.0:
-    print("Alert")
-else:
-    print("Normal")
-```
-Which test reading exposes the boundary defect?</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>The incorrect `&gt;` and the required `&gt;=` differ only at exactly 38.0. At that reading, the current code prints `Normal`, while the rule requires `Alert`. Values above or below the boundary do not distinguish the two operators.</x:v>
-      </x:c>
-      <x:c r="D12" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G12" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>if-else</x:v>
-      </x:c>
-      <x:c r="L12"/>
-      <x:c r="M12" t="str">
-        <x:v>36.5</x:v>
-      </x:c>
-      <x:c r="N12" t="str">
-        <x:v>39.2</x:v>
-      </x:c>
-      <x:c r="O12" t="str">
-        <x:v>41.0</x:v>
-      </x:c>
-      <x:c r="P12" t="str">
-        <x:v>38.0</x:v>
-      </x:c>
-      <x:c r="Q12" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
-        <x:v>Python - MCQ - 3.2.2</x:v>
-      </x:c>
-      <x:c r="B13" t="str">
-        <x:v>A courier charges by weight: under 1 kg is "Light", 1 to 5 kg is "Standard", and over 5 kg is "Heavy":
-```python
-weight = 3.0
-if weight &lt; 1:
-    print("Light")
-elif ________:
-    print("Standard")
-else:
-    print("Heavy")
-```
-Which is the shortest condition that correctly completes the chain?</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>Since `weight &lt; 1` is already ruled out, the value is guaranteed to be 1 or more — no need to re-check the lower end. Only the top edge is left, and 5 is included, so `weight &lt;= 5` is enough. `weight &lt; 5` wrongly pushes 5 into "Heavy"; the others re-test a lower bound that is already certain.</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F13" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G13" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K13" t="str">
-        <x:v>elif-multi-way-branching</x:v>
-      </x:c>
-      <x:c r="L13"/>
-      <x:c r="M13" t="str">
-        <x:v>weight &gt; 1 and weight &lt; 5</x:v>
-      </x:c>
-      <x:c r="N13" t="str">
-        <x:v>weight &lt;= 5</x:v>
-      </x:c>
-      <x:c r="O13" t="str">
-        <x:v>weight &gt;= 1 and weight &lt;= 5</x:v>
-      </x:c>
-      <x:c r="P13" t="str">
-        <x:v>weight &lt; 5</x:v>
-      </x:c>
-      <x:c r="Q13" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
-        <x:v>Python - MCQ - 3.2.3</x:v>
-      </x:c>
-      <x:c r="B14" t="str">
-        <x:v>An age arrives directly from `input()`, so it is text when the comparison runs:
-```python
-age = input("Age: ")
-if age &gt;= 18:
-    print("Eligible")
-else:
-    print("Not eligible")
-```
-Which is the smallest correct repair?</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>`input()` returns text, and text cannot be ordered against the integer 18. Converting at the point of input with `age = int(input("Age: "))` makes both sides numeric before the comparison. Comparing with the text `"18"` would use character ordering rather than numeric age ordering.</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F14" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G14" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K14" t="str">
-        <x:v>input-validation</x:v>
-      </x:c>
-      <x:c r="L14"/>
-      <x:c r="M14" t="str">
-        <x:v>Use `age = str(input("Age: "))`</x:v>
-      </x:c>
-      <x:c r="N14" t="str">
-        <x:v>Use `age = input("Age: ") + 0`</x:v>
-      </x:c>
-      <x:c r="O14" t="str">
-        <x:v>Use `age = int(input("Age: "))`</x:v>
-      </x:c>
-      <x:c r="P14" t="str">
-        <x:v>Change the test to `age &gt;= "18"`</x:v>
-      </x:c>
-      <x:c r="Q14" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
-        <x:v>Python - MCQ - 3.2.4</x:v>
-      </x:c>
-      <x:c r="B15" t="str">
-        <x:v>A library should charge a late fee when a book is kept for more than 14 days. But a book returned after 20 days shows "Returned on time":
-```python
-days = 20
-if days &lt; 14:
-    print("Late fee applies")
-else:
-    print("Returned on time")
-```
-What is wrong with the check?</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>The comparison points the wrong way. `days &lt; 14` is True only for short loans, so a 20-day loan takes the `else` and is called on time. The fee is for *more than* 14 days, so the test should be `days &gt; 14`.</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F15" t="str">
-        <x:v>easy</x:v>
-      </x:c>
-      <x:c r="G15" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
       <x:c r="H15" t="str">
         <x:v>python - Set 2</x:v>
       </x:c>
@@ -1260,42 +1261,41 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>if-else</x:v>
+        <x:v>truthiness-and-boolean-logic</x:v>
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>It should be &gt;= 14 to include the 14th day</x:v>
+        <x:v>`reject = not pin_correct and not account_active`</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>&lt; should be &gt;</x:v>
+        <x:v>`reject = pin_correct or account_active`</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Nothing is wrong</x:v>
+        <x:v>`reject = pin_correct and not account_active`</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>The else branch should print the fee</x:v>
+        <x:v>`reject = not pin_correct or not account_active`</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>Python - MCQ - 3.2.5</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>A weather station should flag any reading below -50 or above 150. But a reading of 200 was called "normal":
+        <x:v>A one-shot command kiosk must recognise its closing command without processing it as ordinary work.
 ```python
-reading = 200
-if reading &lt; -50 and reading &gt; 150:
-    print("Sensor fault")
-else:
-    print("Reading normal")
+command = input("Command: ")
+print(f"Processing {command}")
+if command == "quit":
+    message = "Closing"
 ```
-Why did it not flag 200?</x:v>
+For this one-shot command request, where should the processing line be placed so `"quit"` is not treated as work?</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>One number can never be below -50 AND above 150 at the same time, so the `and` is always False and every reading is called normal. It should be `or`: flag when the reading is below -50 OR above 150.</x:v>
+        <x:v>Ordinary processing belongs in the mutually exclusive alternative to the sentinel branch.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>8</x:v>
@@ -1307,7 +1307,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>python - Set 2</x:v>
@@ -1319,53 +1319,47 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>The comparisons are backwards</x:v>
+        <x:v>Before the input line</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>and should be or</x:v>
+        <x:v>Inside the `if command == "quit"` block</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>The else needs its own condition</x:v>
+        <x:v>In an `else` paired with `if command == "quit"`</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>Both &lt; and &gt; should become &lt;= and &gt;=</x:v>
+        <x:v>After the entire loop</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 3.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A player shows 4K only for a premium user on a line faster than 25 Mbps. This user is premium, but the line is only 18 Mbps:
-```python
-premium = True
-bandwidth = 18
-quality = "4K" if premium and bandwidth &gt; 25 else "HD"
-print(quality)
-```
-What is quality set to?</x:v>
+        <x:v>A support tool routes one typed command among a small fixed set of operations.
+One variable will contain exactly one of the fixed commands `"start"`, `"stop"`, or `"help"`, with a fallback for all other text. Select the clearest Unit 3 structure.</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>The condition is `premium and bandwidth &gt; 25`. `premium` is True but `bandwidth &gt; 25` is `18 &gt; 25` → False, so `True and False` → False. The expression takes the `else` value, `"HD"`. Both parts of the `and` must be True to get 4K.</x:v>
+        <x:v>`match`/`case` clearly expresses comparison of one value against several fixed alternatives.</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1377,58 +1371,47 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>conditional-ternary-expressions</x:v>
+        <x:v>match-case</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>4K — being premium is enough</x:v>
+        <x:v>`match`/`case` ending in `case _`</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>An error — you cannot use and inside a ternary</x:v>
+        <x:v>A nested conditional expression</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>4K — the second part of the and is ignored</x:v>
+        <x:v>Independent numeric range checks</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>HD — the line is not faster than 25, so the and is False</x:v>
+        <x:v>One `if` with arithmetic operators</x:v>
       </x:c>
       <x:c r="Q17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 3.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>A lift moves only when the doors are shut, and even then it refuses if the load is over 800 kg. Right now the doors are shut and the load is 850 kg:
-```python
-doors_closed = True
-weight = 850
-if doors_closed:
-    if weight &lt;= 800:
-        print("Lift moving")
-    else:
-        print("Overloaded")
-else:
-    print("Doors open")
-```
-Which one message shows?</x:v>
+        <x:v>An analytics report calculates an average only when at least one observation exists.
+`total / count` must be evaluated only when `count` is non-zero. Select the safe condition.</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>The doors are shut, so the outer `if` runs. Inside, `weight &lt;= 800` is `850 &lt;= 800` → False, so the inner `else` runs and shows `Overloaded`. The outer `else` ("Doors open") belongs to the door check and is skipped.</x:v>
+        <x:v>A zero count makes the first part of `and` false, so Python short-circuits before division.</x:v>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E18" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F18" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H18" t="str">
         <x:v>python - Set 2</x:v>
@@ -1440,43 +1423,44 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>nested-conditions-and-guard-clauses</x:v>
+        <x:v>truthiness-and-boolean-logic</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>Overloaded</x:v>
+        <x:v>`if total / count &gt; 80 and count != 0:`</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Lift moving</x:v>
+        <x:v>`if count == 0 or total / count &gt; 80:`</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Doors open</x:v>
+        <x:v>`if total &gt; 80 or count:`</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Both Overloaded and Doors open</x:v>
+        <x:v>`if count != 0 and total / count &gt; 80:`</x:v>
       </x:c>
       <x:c r="Q18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 3.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>A gym gate opens only for a member who is active and has not already entered — so one pass cannot be used twice. This member is active and has not entered yet:
+        <x:v>A canteen menu needs a dependable response when a user enters an unsupported choice.
 ```python
-active = True
-checked_in = False
-if ________:
-    print("Access granted")
-else:
-    print("Access denied")
+match choice:
+    case "1":
+        item = "Tea"
+    case "2":
+        item = "Coffee"
+    __________
+        item = "Invalid"
 ```
-Which condition opens the gate now but blocks a second entry?</x:v>
+Complete the router so every other value is handled.</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Both parts must be true: the member is active, and they have not entered (`not checked_in`). Here `active and not checked_in` → `True and not False` → `True and True` → True, so the gate opens. If they had already entered, `not checked_in` would be False and the gate would stay shut.</x:v>
+        <x:v>In `match`, the wildcard pattern `_` is the catch-all equivalent of a final `else`.</x:v>
       </x:c>
       <x:c r="D19" t="n">
         <x:v>8</x:v>
@@ -1500,538 +1484,531 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
+        <x:v>match-case</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>active or not checked_in</x:v>
+        <x:v>`else:`</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>active and checked_in</x:v>
+        <x:v>`case _:`</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>not active and not checked_in</x:v>
+        <x:v>`case else:`</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>active and not checked_in</x:v>
+        <x:v>`default:`</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="198" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>Python - MCQ - 3.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A coder rewrote a four-line decision as a single line, and a reviewer says the meaning flipped. The applicant's score is 720:
+        <x:v>A tutoring portal uses two independent score checks that may both produce feedback.
+```python
+score = 45
+if score &gt;= 40:
+    print("Pass")
+if score &lt;= 50:
+    print("Support")
+else:
+    print("Independent")
+```
+Select the exact transcript, preserving line order.</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Both independent `if` conditions are true; the `else` belongs only to the second `if` and is skipped.</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>conditional-statements</x:v>
+      </x:c>
+      <x:c r="L20"/>
+      <x:c r="M20" t="str">
+        <x:v>`Support` only</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>`Pass` followed by `Independent`</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>`Pass` followed by `Support`</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>`Pass` only</x:v>
+      </x:c>
+      <x:c r="Q20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="132" hidden="0" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>Python - MCQ - 3.2.10</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>A payment-approval module was submitted with both punctuation and indentation defects.
+```python
+if balance &gt;= amount
+print("Approved")
+else:
+    print("Declined")
+```
+Which patch fixes every syntax/indentation problem while preserving the two-way decision?</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>The condition needs a colon, and the true action must be indented as the `if` block.</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>analyze</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>conditional-statements</x:v>
+      </x:c>
+      <x:c r="L21"/>
+      <x:c r="M21" t="str">
+        <x:v>```python
+if balance &gt;= amount:
+    print("Approved")
+else:
+    print("Declined")
+```</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>Add only a colon after `amount`.</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>Indent only the `else` line.</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>Replace `else` with `elif:`.</x:v>
+      </x:c>
+      <x:c r="Q21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Python - MCQ - 3.2.11</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>A parcel service assigns a shipping category to a package exactly on its weight boundary.
+```python
+weight = 5
+category = "Heavy" if weight &gt; 5 else "Standard"
+```
+Complete the dry-run record.</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Five is not greater than five, so the false-side value is selected.</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>understand</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>conditional-expressions</x:v>
+      </x:c>
+      <x:c r="L22"/>
+      <x:c r="M22" t="str">
+        <x:v>Condition: true; category: `"Heavy"`</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>Condition: false; category: `"Standard"`</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>Condition: false; category: `"Heavy"`</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>Condition: true; category: `"Standard"`</x:v>
+      </x:c>
+      <x:c r="Q22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>Python - MCQ - 3.2.12</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>A scholarship portal updates an applicant's status through an outer eligibility check and an inner verification check.
+```python
+points = 70
+verified = False
+status = "Review"
+if points &gt;= 60:
+    status = "Eligible"
+    if not verified:
+        status = "Verify first"
+else:
+    status = "Rejected"
+```
+Select the path taken from start to finish.</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>The outer condition passes, assigning `Eligible`; the inner condition also passes and overwrites it with `Verify first`.</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>nested-conditions</x:v>
+      </x:c>
+      <x:c r="L23"/>
+      <x:c r="M23" t="str">
+        <x:v>`Review → Rejected`</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>`Review → Verify first → Eligible`</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>`Review → Rejected → Verify first`</x:v>
+      </x:c>
+      <x:c r="P23" t="str">
+        <x:v>`Review → Eligible → Verify first`</x:v>
+      </x:c>
+      <x:c r="Q23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>Python - MCQ - 3.2.13</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>A college event team has written its admission policy in words and needs an exact Boolean translation.
+Policy: “An ID is mandatory, and the student must additionally be registered or appear on the guest list.”</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>`has_id` is required in every successful case; the two alternative qualifications are grouped together.</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>truthiness-and-boolean-logic</x:v>
+      </x:c>
+      <x:c r="L24"/>
+      <x:c r="M24" t="str">
+        <x:v>`has_id and (registered or on_guest_list)`</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>`has_id or registered and on_guest_list`</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>`(has_id and registered) and on_guest_list`</x:v>
+      </x:c>
+      <x:c r="P24" t="str">
+        <x:v>`has_id or registered or on_guest_list`</x:v>
+      </x:c>
+      <x:c r="Q24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="132" hidden="0" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>Python - MCQ - 3.2.14</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>An exam-results page promises one outcome, but two inclusive rules may overlap.
+```python
+if marks &gt;= 40:
+    print("Pass")
+if marks &lt;= 40:
+    print("Fail")
+```
+Select the input that makes both statements execute.</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Forty satisfies both inclusive comparisons, exposing the overlap between the independent conditions.</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>understand</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>conditional-statements</x:v>
+      </x:c>
+      <x:c r="L25"/>
+      <x:c r="M25" t="str">
+        <x:v>`39`</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>`41`</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>`40`</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>`100`</x:v>
+      </x:c>
+      <x:c r="Q25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>Python - MCQ - 3.2.15</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>A configuration router cannot start because its `match` block was indented and punctuated incorrectly.
+```python
+match mode:
+    case "safe"
+    result = "Safe"
+    case _:
+    result = "Unknown"
+```
+Select the patch that fixes every syntax and block-structure problem.</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Each `case` needs a colon, both cases align beneath `match`, and each action is indented beneath its case.</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>match-case</x:v>
+      </x:c>
+      <x:c r="L26"/>
+      <x:c r="M26" t="str">
+        <x:v>Add a colon after `case "safe"` only.</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>Indent both `case` lines under the assignments.</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>Replace `case _:` with `else:` and change nothing else.</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>```python
+match mode:
+    case "safe":
+        result = "Safe"
+    case _:
+        result = "Unknown"
+```</x:v>
+      </x:c>
+      <x:c r="Q26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>Python - MCQ - 3.2.16</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>A payment service performs several actions on success and several different actions on failure.
+A payment-success branch must update the balance, create a receipt, and write an audit entry; failure must record a reason. Choose the most maintainable structure.</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Conditional expressions suit simple value selection. Multiple branch-specific actions belong in a full statement.</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>control-flow</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>conditional-expressions</x:v>
+      </x:c>
+      <x:c r="L27"/>
+      <x:c r="M27" t="str">
+        <x:v>A three-level nested conditional expression</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>A full `if`/`else` with the relevant actions grouped in each block</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>Two unrelated `if` statements that can both run</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>`match` against every possible balance</x:v>
+      </x:c>
+      <x:c r="Q27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>Python - MCQ - 3.2.17</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>A shop is deciding whether member and coupon discounts should stack when both are earned.
 ```python
 # Version A
-if score &gt;= 700:
-    decision = "Approved"
-else:
-    decision = "Rejected"
+discount = 0
+if member:
+    discount += 50
+if coupon:
+    discount += 50
 # Version B
-decision = "Rejected" if score &gt;= 700 else "Approved"
+discount = 0
+if member:
+    discount += 50
+elif coupon:
+    discount += 50
 ```
-What does each version store for score = 720?</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>In Version A, `720 &gt;= 700` is True, so `decision = "Approved"`. In Version B the labels are the wrong way round: when the condition is True it returns `"Rejected"`. So the two disagree — the reviewer is right. A correct one-liner would read `"Approved" if score &gt;= 700 else "Rejected"`.</x:v>
-      </x:c>
-      <x:c r="D20" t="n">
+Under which input do the final discounts differ?</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Independent `if` statements stack both discounts; the `elif` version stops after the member branch.</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E20" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
+      <x:c r="E28" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
         <x:v>medium</x:v>
       </x:c>
-      <x:c r="G20" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>conditional-ternary-expressions</x:v>
-      </x:c>
-      <x:c r="L20"/>
-      <x:c r="M20" t="str">
-        <x:v>Version A stores "Approved", Version B stores "Rejected"</x:v>
-      </x:c>
-      <x:c r="N20" t="str">
-        <x:v>Both store "Approved"</x:v>
-      </x:c>
-      <x:c r="O20" t="str">
-        <x:v>Both store "Rejected"</x:v>
-      </x:c>
-      <x:c r="P20" t="str">
-        <x:v>Version A stores "Rejected", Version B stores "Approved"</x:v>
-      </x:c>
-      <x:c r="Q20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>Python - MCQ - 3.2.10</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>A post office charges: up to 250 g → ₹20, 251 to 500 g → ₹40, over 500 g → ₹60. A 500 g parcel is being charged ₹60 instead of ₹40:
-```python
-grams = 500
-if grams &lt;= 250:
-    cost = 20
-elif grams &lt; 500:
-    cost = 40
-else:
-    cost = 60
-print(cost)
-```
-Which single smallest change fixes the 500 g parcel?</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>The middle band uses `grams &lt; 500`, so exactly 500 fails it and drops to the `else`, costing ₹60. The ₹40 band is meant to include 500, so changing `&lt; 500` to `&lt;= 500` is the smallest fix. Reordering or touching the 250 line does not help, and turning the `else` into `grams &gt; 500` would leave 500 matching no branch at all.</x:v>
-      </x:c>
-      <x:c r="D21" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I21" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K21" t="str">
-        <x:v>elif-multi-way-branching</x:v>
-      </x:c>
-      <x:c r="L21"/>
-      <x:c r="M21" t="str">
-        <x:v>Put the else first</x:v>
-      </x:c>
-      <x:c r="N21" t="str">
-        <x:v>Change grams &lt;= 250 to grams &lt; 250</x:v>
-      </x:c>
-      <x:c r="O21" t="str">
-        <x:v>Change the else to elif grams &gt; 500</x:v>
-      </x:c>
-      <x:c r="P21" t="str">
-        <x:v>Change grams &lt; 500 to grams &lt;= 500</x:v>
-      </x:c>
-      <x:c r="Q21" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>Python - MCQ - 3.2.11</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>A dashboard has mutually exclusive rating bands and needs a clear fallback for any value not covered explicitly. Which structure communicates that design most directly?</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>An `if`-`elif`-`else` chain makes the mutual exclusivity explicit: the first matching band runs and the final `else` provides a fallback. Carefully written separate `if` statements could also be mutually exclusive, but the chain expresses the intended one-path design more clearly and is safer to maintain.</x:v>
-      </x:c>
-      <x:c r="D22" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>understand</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>elif-multi-way-branching</x:v>
-      </x:c>
-      <x:c r="L22"/>
-      <x:c r="M22" t="str">
-        <x:v>An `if`-`elif`-`else` chain</x:v>
-      </x:c>
-      <x:c r="N22" t="str">
-        <x:v>Three unrelated `if` statements</x:v>
-      </x:c>
-      <x:c r="O22" t="str">
-        <x:v>One `if` joining every band with `or`</x:v>
-      </x:c>
-      <x:c r="P22" t="str">
-        <x:v>A `match` comparing every possible rating</x:v>
-      </x:c>
-      <x:c r="Q22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>Python - MCQ - 3.2.12</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>A data plan charges: up to 2 GB is free, up to 10 GB is ₹100, over 10 GB is ₹300. A user on 1.5 GB — clearly free — was charged ₹100:
-```python
-gb = 1.5
-if gb &lt;= 10:
-    charge = 100
-elif gb &lt;= 2:
-    charge = 0
-else:
-    charge = 300
-print(charge)
-```
-Why was the free user charged?</x:v>
-      </x:c>
-      <x:c r="C23" t="str">
-        <x:v>`gb &lt;= 10` is True for anything up to 10 GB, including 1.5 GB, so the first branch runs and charges ₹100. The `elif gb &lt;= 2` can never be reached for any value at or below 10. Range checks must go from smallest to largest: test `&lt;= 2` first, then `&lt;= 10`, then `else`.</x:v>
-      </x:c>
-      <x:c r="D23" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F23" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G23" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H23" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I23" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J23" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K23" t="str">
-        <x:v>elif-multi-way-branching</x:v>
-      </x:c>
-      <x:c r="L23"/>
-      <x:c r="M23" t="str">
-        <x:v>The order is wrong</x:v>
-      </x:c>
-      <x:c r="N23" t="str">
-        <x:v>The else should say gb &gt; 10</x:v>
-      </x:c>
-      <x:c r="O23" t="str">
-        <x:v>Every &lt;= should be &lt;</x:v>
-      </x:c>
-      <x:c r="P23" t="str">
-        <x:v>The free and top tiers need a lower bound with and</x:v>
-      </x:c>
-      <x:c r="Q23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
-        <x:v>Python - MCQ - 3.2.13</x:v>
-      </x:c>
-      <x:c r="B24" t="str">
-        <x:v>A lock should say "Invalid card" when a valid card is used with the wrong PIN. Instead it stays completely silent:
-```python
-card_valid = True
-pin = "0000"
-if card_valid:
-    if pin == "1234":
-        print("Unlocked")
-else:
-    print("Invalid card")
-```
-What does this print for a valid card and the wrong PIN?</x:v>
-      </x:c>
-      <x:c r="C24" t="str">
-        <x:v>The `else` lines up with the outer `if card_valid`, not the PIN check. The card is valid, so that `else` is skipped. Inside, `pin == "1234"` is False, so nothing runs there either — hence the silence. A wrong PIN needs its own `else` under the inner `if`.</x:v>
-      </x:c>
-      <x:c r="D24" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F24" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="G24" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H24" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I24" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J24" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K24" t="str">
-        <x:v>nested-conditions-and-guard-clauses</x:v>
-      </x:c>
-      <x:c r="L24"/>
-      <x:c r="M24" t="str">
-        <x:v>Invalid card</x:v>
-      </x:c>
-      <x:c r="N24" t="str">
-        <x:v>Unlocked</x:v>
-      </x:c>
-      <x:c r="O24" t="str">
-        <x:v>Nothing</x:v>
-      </x:c>
-      <x:c r="P24" t="str">
-        <x:v>Both Unlocked and Invalid card</x:v>
-      </x:c>
-      <x:c r="Q24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
-        <x:v>Python - MCQ - 3.2.14</x:v>
-      </x:c>
-      <x:c r="B25" t="str">
-        <x:v>A kiosk matches typed language codes, which are all written in lowercase. A traveller types "EN":
-```python
-lang = "EN"
-match lang:
-    case "en":
-        print("English selected")
-    case "hi":
-        print("Hindi selected")
-    case "ta":
-        print("Tamil selected")
-    case _:
-        print("Language not supported")
-```
-What prints, and why?</x:v>
-      </x:c>
-      <x:c r="C25" t="str">
-        <x:v>`match-case` compares for an exact match, and capital letters count. `"EN"` does not equal `"en"`, `"hi"`, or `"ta"`, so none of the named cases match and `case _` runs, printing `Language not supported`. Using `lang.lower()` first would fix it.</x:v>
-      </x:c>
-      <x:c r="D25" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F25" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G25" t="str">
-        <x:v>understand</x:v>
-      </x:c>
-      <x:c r="H25" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I25" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J25" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K25" t="str">
-        <x:v>match-case</x:v>
-      </x:c>
-      <x:c r="L25"/>
-      <x:c r="M25" t="str">
-        <x:v>English selected — match ignores capitals</x:v>
-      </x:c>
-      <x:c r="N25" t="str">
-        <x:v>Language not supported — "EN" does not equal "en", so no case matches</x:v>
-      </x:c>
-      <x:c r="O25" t="str">
-        <x:v>Nothing — match errors when no case matches</x:v>
-      </x:c>
-      <x:c r="P25" t="str">
-        <x:v>English selected — the _ case jumps to the first case</x:v>
-      </x:c>
-      <x:c r="Q25" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
-        <x:v>Python - MCQ - 3.2.15</x:v>
-      </x:c>
-      <x:c r="B26" t="str">
-        <x:v>A form should block a blank subject. But a ticket goes through even when the subject is just two spaces:
-```python
-subject = "  "
-if subject:
-    print("Ticket created")
-else:
-    print("Subject required")
-```
-What happens, and why?</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>For a string, only the empty string `""` is falsy. `"  "` has two space characters, so it is not empty and counts as truthy — the ticket is created. To block spaces-only input, the developer should test `if subject.strip():`.</x:v>
-      </x:c>
-      <x:c r="D26" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F26" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G26" t="str">
-        <x:v>understand</x:v>
-      </x:c>
-      <x:c r="H26" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I26" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J26" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K26" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
-      </x:c>
-      <x:c r="L26"/>
-      <x:c r="M26" t="str">
-        <x:v>Subject required — a string of only spaces counts as empty</x:v>
-      </x:c>
-      <x:c r="N26" t="str">
-        <x:v>Ticket created — spaces still count as characters, so the string is not empty</x:v>
-      </x:c>
-      <x:c r="O26" t="str">
-        <x:v>An error — spaces cannot be tested in an if</x:v>
-      </x:c>
-      <x:c r="P26" t="str">
-        <x:v>Subject required — Python removes the spaces first</x:v>
-      </x:c>
-      <x:c r="Q26" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>Python - MCQ - 3.2.16</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>A dispatcher checks a robot in order. Right now it has an order but no free slot yet:
-```python
-has_order = True
-slot_free = False
-zone = ""
-if has_order and slot_free:
-    print("Robot dispatched")
-elif has_order and not slot_free:
-    print("Order queued — waiting for a slot")
-elif not has_order and zone:
-    print("Idle move to zone")
-else:
-    print("Robot idle")
-```
-Which one line prints?</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>First test: `has_order and slot_free` → `True and False` → False. Next: `has_order and not slot_free` → `True and True` → True, so it prints `Order queued — waiting for a slot`. Once a branch runs, the rest are skipped; the empty `zone` is never even checked.</x:v>
-      </x:c>
-      <x:c r="D27" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G27" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I27" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J27" t="str">
-        <x:v>control-flow</x:v>
-      </x:c>
-      <x:c r="K27" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
-      </x:c>
-      <x:c r="L27"/>
-      <x:c r="M27" t="str">
-        <x:v>Robot idle</x:v>
-      </x:c>
-      <x:c r="N27" t="str">
-        <x:v>Idle move to zone</x:v>
-      </x:c>
-      <x:c r="O27" t="str">
-        <x:v>Order queued</x:v>
-      </x:c>
-      <x:c r="P27" t="str">
-        <x:v>Robot dispatched</x:v>
-      </x:c>
-      <x:c r="Q27" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
-        <x:v>Python - MCQ - 3.2.17</x:v>
-      </x:c>
-      <x:c r="B28" t="str">
-        <x:v>A quiz records every result, but prints `Passed` only for scores of 50 or more:
-```python
-score = 45
-if score &gt;= 50:
-    print("Passed")
-print("Result recorded")
-```
-What does the program print?</x:v>
-      </x:c>
-      <x:c r="C28" t="str">
-        <x:v>`score &gt;= 50` is False, so Python skips the indented `print("Passed")`. The final print is outside the `if` block, so it still runs. The program prints only `Result recorded`.</x:v>
-      </x:c>
-      <x:c r="D28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F28" t="str">
-        <x:v>easy</x:v>
-      </x:c>
       <x:c r="G28" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H28" t="str">
         <x:v>python - Set 2</x:v>
@@ -2043,54 +2020,53 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>the-if-statement</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>Passed only</x:v>
+        <x:v>Both are false.</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>Nothing</x:v>
+        <x:v>Only `member` is true.</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Result recorded only</x:v>
+        <x:v>Both are true.</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Passed, then Result recorded</x:v>
+        <x:v>Only `coupon` is true.</x:v>
       </x:c>
       <x:c r="Q28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="132" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Python - MCQ - 3.2.18</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A clinic calls a reading "Normal" only from 90 to 120, and both 90 and 120 themselves count as normal:
+        <x:v>A signup form must reject names made only of spaces while accepting names with surrounding whitespace.
+A required name may contain surrounding spaces but may not consist only of spaces:
 ```python
-systolic = 110
-if ________:
-    print("Normal")
+if __________:
+    result = "Accepted"
 else:
-    print("Check with doctor")
-```
-Which condition keeps 90 and 120 as normal, without calling every value normal?</x:v>
+    result = "Name required"
+```</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>The band includes both ends, and Python lets you chain it as `90 &lt;= systolic &lt;= 120`. Line A uses strict `&lt;`/`&gt;` and wrongly drops 90 and 120; line B with `or` is true for every number; line C can only be true if one value equals both 90 and 120, which is impossible.</x:v>
+        <x:v>`.strip()` turns whitespace-only input into the falsy empty string while leaving real content non-empty.</x:v>
       </x:c>
       <x:c r="D29" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>apply</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H29" t="str">
         <x:v>python - Set 2</x:v>
@@ -2102,44 +2078,41 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>the-if-statement</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>systolic &gt; 90 and systolic &lt; 120</x:v>
+        <x:v>`name.strip()`</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>90 &lt;= systolic &lt;= 120</x:v>
+        <x:v>`name == True`</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>systolic &gt;= 90 or systolic &lt;= 120</x:v>
+        <x:v>`not name`</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>systolic == 90 and systolic == 120</x:v>
+        <x:v>`name.isdigit()`</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="132" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Python - MCQ - 3.2.19</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>A colleague says one line in this shipping code can never run, whatever the tier is:
+        <x:v>A score-import service is incorrectly accepting every numeric value as valid.
 ```python
-tier = "gold"
-if tier == "gold":
-    print("Free next-day delivery")
-elif tier == "gold":
-    print("Free standard delivery")
+if score &gt;= 0 or score &lt;= 100:
+    result = "Valid"
 else:
-    print("Paid delivery")
+    result = "Invalid"
 ```
-Which line can never run, and what does a "gold" customer see?</x:v>
+Complete the reviewer comment: “The interval requires _____ because _____.”</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>The `elif` repeats the exact test of the `if`. If the `if` is True, the `elif` is never reached; if the `if` is False, the same `elif` is also False. So the second line can never run. For `"gold"`, the `if` runs and shows `Free next-day delivery`.</x:v>
+        <x:v>Membership in a closed interval requires satisfying the lower and upper limits simultaneously.</x:v>
       </x:c>
       <x:c r="D30" t="n">
         <x:v>8</x:v>
@@ -2151,7 +2124,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>python - Set 2</x:v>
@@ -2163,49 +2136,52 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>elif-multi-way-branching</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>The else</x:v>
+        <x:v>`or`; either boundary is optional</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>The if and the elif both</x:v>
+        <x:v>`and`; both boundary comparisons must hold</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>The second branch</x:v>
+        <x:v>`not`; every valid score is falsy</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>None</x:v>
+        <x:v>`==`; ranges use equality only</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Python - MCQ - 3.2.20</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>A quiz marks a score of exactly 60 as "Qualified" — 60 counts as a pass. Of the lines below, one fails a score of exactly 60, one is not valid syntax, and one swaps the labels:
+        <x:v>A reporting job fails while calculating an average for an empty dataset.
 ```python
-score = 60
-status = ________
-print(status)
+count = 0
+total = 90
+if total / count &gt; 80 and count != 0:
+    result = "High"
+else:
+    result = "Unavailable"
 ```
-Which line is correct?</x:v>
+What happens before either assignment is reached?</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Since 60 passes, the test needs `&gt;=`, with the labels in the right order: `"Qualified" if score &gt;= 60 else "Try again"`. Line A uses `&gt;`, which fails a score of exactly 60; line C is statement syntax, not an expression; line D puts the labels the wrong way round.</x:v>
+        <x:v>Python evaluates the left operand of `and` first. The unsafe division occurs before the zero check can help.</x:v>
       </x:c>
       <x:c r="D31" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G31" t="str">
         <x:v>apply</x:v>
@@ -2220,49 +2196,44 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>conditional-ternary-expressions</x:v>
+        <x:v>truthiness-and-boolean-logic</x:v>
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31" t="str">
-        <x:v>"Qualified" if score &gt; 60 else "Try again"</x:v>
+        <x:v>`count != 0` becomes false and safely skips division.</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>if score &gt;= 60: "Qualified" else: "Try again"</x:v>
+        <x:v>`result` becomes `"Unavailable"`.</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>"Try again" if score &gt;= 60 else "Qualified"</x:v>
+        <x:v>The condition becomes true because `total` is 90.</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>"Qualified" if score &gt;= 60 else "Try again"</x:v>
+        <x:v>`total / count` raises `ZeroDivisionError` because it is evaluated first.</x:v>
       </x:c>
       <x:c r="Q31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>Python - MCQ - 3.2.21</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>A store should alert to reorder when stock drops below 20, but stay quiet when stock is exactly 20. The stock below is exactly 20:
-```python
-stock = 20
-if ________:
-    print("Reorder now")
-```
-Which condition stays quiet at 20 but would alert at 19?</x:v>
+        <x:v>A university grader must classify overlapping score thresholds without allowing a broad rule to hide a higher grade.
+The grade thresholds are `A: &gt;= 90`, `B: &gt;= 75`, `C: &gt;= 40`, otherwise `F`. Choose the only safe top-to-bottom order.</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>"Below 20" means strictly less than 20, so `stock &lt; 20` is `20 &lt; 20` → False and stays quiet, while 19 would alert. `stock &lt;= 20` would wrongly alert at 20, `stock &gt; 20` reverses the rule, and `stock == 20` matches only 20.</x:v>
+        <x:v>In an `elif` chain, the first true branch wins, so overlapping thresholds must descend from highest to lowest.</x:v>
       </x:c>
       <x:c r="D32" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E32" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G32" t="str">
         <x:v>apply</x:v>
@@ -2277,47 +2248,45 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>the-if-statement</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
-        <x:v>stock &lt; 20</x:v>
+        <x:v>`&gt;= 90`, `&gt;= 75`, `&gt;= 40`, `else`</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>stock &lt;= 20</x:v>
+        <x:v>`&gt;= 40`, `&gt;= 75`, `&gt;= 90`, `else`</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>stock &gt; 20</x:v>
+        <x:v>`else`, `&gt;= 40`, `&gt;= 75`, `&gt;= 90`</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>stock == 20</x:v>
+        <x:v>`&gt;= 75`, `&gt;= 40`, `&gt;= 90`, `else`</x:v>
       </x:c>
       <x:c r="Q32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="198" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Python - MCQ - 3.2.22</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>A reviewer worries the two-`if` heater code might set the value twice, or disagree with the `if`/`else` version for some temperature:
+        <x:v>A learning platform applies several independent badge rules to the same score.
 ```python
-# Version A
-if temp &lt; 18:
-    heater = "ON"
-else:
-    heater = "OFF"
-# Version B
-if temp &lt; 18:
-    heater = "ON"
-if temp &gt;= 18:
-    heater = "OFF"
+score = 85
+badge = "None"
+if score &gt;= 50:
+    badge = "Pass"
+if score &gt;= 80:
+    badge = "Distinction"
+if score == 100:
+    badge = "Perfect"
 ```
-The two conditions are opposites. Can the versions ever give different results?</x:v>
+Select the correct transition sequence.</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>For any temperature, exactly one of `temp &lt; 18` and `temp &gt;= 18` is True — they are exact opposites that cover every case. So both versions set the same value every time. Version A is still safer, because an `else` cannot drift out of step during later edits.</x:v>
+        <x:v>The first two conditions are true and overwrite the value in order; the exact-100 check is false.</x:v>
       </x:c>
       <x:c r="D33" t="n">
         <x:v>8</x:v>
@@ -2329,7 +2298,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>python - Set 2</x:v>
@@ -2341,48 +2310,35 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>if-else</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33" t="str">
-        <x:v>Yes — they differ at temp == 18</x:v>
+        <x:v>`None → Perfect`</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Yes — they differ at temp == 17</x:v>
+        <x:v>`None → Pass → Perfect`</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>No — one of the two opposite conditions is always true, so both set the same value</x:v>
+        <x:v>`None → Pass → Distinction`</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Yes — two ifs always set the value twice</x:v>
+        <x:v>`None → Distinction → Pass`</x:v>
       </x:c>
       <x:c r="Q33" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>Python - MCQ - 3.2.23</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>These two fraud checks look the same, but notice that Version A's inner `if` has an `else`. A reviewer tries both with a small ₹5000 payment:
-```python
-# Version A
-if amount &gt; 10000:
-    if foreign:
-        print("Flag for review")
-    else:
-        print("Domestic large payment")
-# Version B
-if amount &gt; 10000 and foreign:
-    print("Flag for review")
-else:
-    print("Domestic large payment")
-```
-For the ₹5000 payment, do they give the same result?</x:v>
+        <x:v>A weather form accepts signed temperatures but must never convert malformed text prematurely.
+A temperature form should accept whole numbers from -50 through 60. Which approach safely handles `"-5"`, `"12"`, and malformed text without exception handling?</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>No. For ₹5000, Version A's outer `if` is False, so nothing prints. Version B's combined test is also False, so its `else` runs and prints `Domestic large payment`. Version A's inner `else` only covers a large payment that is not foreign; Version B's `else` covers everything the combined test misses.</x:v>
+        <x:v>`.isdigit()` alone rejects a minus sign. Checking the text shape first prevents unsafe conversion while permitting signed integers.</x:v>
       </x:c>
       <x:c r="D34" t="n">
         <x:v>10</x:v>
@@ -2394,7 +2350,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H34" t="str">
         <x:v>python - Set 2</x:v>
@@ -2406,48 +2362,45 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>nested-conditions-and-guard-clauses</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
-        <x:v>Yes — they always match</x:v>
+        <x:v>Convert with `int(raw)` before any condition.</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>No — Version A flags small foreign payments</x:v>
+        <x:v>Use only `raw.isdigit()`, which accepts the minus sign.</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>No — Version A prints nothing, but Version B prints Domestic large payment</x:v>
+        <x:v>Accept every non-empty string and convert it.</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>No — Version B never checks foreign</x:v>
+        <x:v>Remove one optional leading `-` for the digit check, convert only if the remaining text is digits, then apply the range check.</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="198" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>Python - MCQ - 3.2.24</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>A parking gate reads the vehicle type "bike" and runs it through this match block:
+        <x:v>A canteen kiosk keeps menu input as text, but its `match` cases were written as numbers.
 ```python
-vehicle = "bike"
-match vehicle:
-    case "car":
-        fee = 50
-    case "bike":
-        fee = 20
-    case "truck":
-        fee = 100
+choice = input("Choose 1 or 2: ")
+match choice:
+    case 1:
+        item = "Tea"
+    case 2:
+        item = "Coffee"
     case _:
-        fee = 0
-print(fee)
+        item = "Invalid"
 ```
-What is fee just before it prints?</x:v>
+The program should keep `choice` as text. Select the repair.</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>`match` checks each case from top to bottom for an exact match and runs the first one that fits. `"bike"` matches the second case, so `fee = 20`. The `case _` default is only used when no named case matches.</x:v>
+        <x:v>`input()` returns strings, so the fixed patterns must also be strings when no conversion is performed.</x:v>
       </x:c>
       <x:c r="D35" t="n">
         <x:v>5</x:v>
@@ -2459,7 +2412,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>python - Set 2</x:v>
@@ -2475,38 +2428,37 @@
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>0</x:v>
+        <x:v>Remove `match` and leave no decision.</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>50</x:v>
+        <x:v>Change the cases to `case "1":` and `case "2":`.</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>100</x:v>
+        <x:v>Change `case _` to `else`.</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>20</x:v>
+        <x:v>Compare `choice` with Boolean values.</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="132" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>Python - MCQ - 3.2.25</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>An ATM checks the typed amount before turning it into a number. The field holds "50x":
+        <x:v>An inventory form must reject quantities outside its supported ordering range.
+Valid quantities are 1 through 10:
 ```python
-entry = "50x"
-if not entry.isdigit():
-    print("Enter numbers only")
+if __________:
+    result = "Invalid"
 else:
-    print("Processing", int(entry))
-```
-What does the code do?</x:v>
+    result = "Accepted"
+```</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>`"50x".isdigit()` is False because the text is not all digits, so `not False` → True and the guard runs, printing `Enter numbers only`. The `int(entry)` on the `else` side never runs — which is exactly the crash the check prevents.</x:v>
+        <x:v>A value is invalid when it lies below the lower bound or above the upper bound; endpoints remain valid.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>8</x:v>
@@ -2534,41 +2486,31 @@
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>Prints Processing 50</x:v>
+        <x:v>`quantity &lt; 1 and quantity &gt; 10`</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Crashes on int() with an error</x:v>
+        <x:v>`1 &lt; quantity &lt; 10`</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Prints Processing 50x</x:v>
+        <x:v>`quantity &lt; 1 or quantity &gt; 10`</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Prints Enter numbers only</x:v>
+        <x:v>`quantity &lt;= 1 or quantity &gt;= 10`</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>Python - MCQ - 3.2.26</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>An uploader checks its rules in order for an 8 MB file named "report.pdf". The size limit is 5 MB:
-```python
-name = "report.pdf"
-size = 8
-if not name:
-    print("File name required")
-elif size &gt; 5:
-    print("File too large")
-else:
-    print("Upload accepted")
-```
-Which check stops the upload, and what prints?</x:v>
+        <x:v>A grade classifier groups numeric ranges rather than matching a few fixed commands.
+A teammate proposes fixed literal `case` entries to classify every possible mark from 0 to 100. Approve the clearer alternative.</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>The first check `not name` is False, because `"report.pdf"` is a non-empty (truthy) name. The `elif size &gt; 5` is `8 &gt; 5` → True, so it runs and prints `File too large`. The `else` runs only when both checks pass.</x:v>
+        <x:v>The Unit 3 use of `match` suits fixed options; ordered comparisons are clearer for ranges and thresholds.</x:v>
       </x:c>
       <x:c r="D37" t="n">
         <x:v>8</x:v>
@@ -2580,7 +2522,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H37" t="str">
         <x:v>python - Set 2</x:v>
@@ -2592,56 +2534,56 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>input-validation</x:v>
+        <x:v>match-case</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>Nothing stops it</x:v>
+        <x:v>An ordered `if`/`elif`/`else` chain using range comparisons</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>The name check stops it</x:v>
+        <x:v>One hundred and one separate literal cases</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>The size check stops it</x:v>
+        <x:v>Two unrelated `if` statements for all grades</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>It crashes comparing size to 5</x:v>
+        <x:v>A nested conditional expression containing every threshold</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Python - MCQ - 3.2.27</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>A menu handles choices `"1"` and `"2"`, but it has no catch-all case. The user enters `"9"`:
+        <x:v>An age-signup form handles empty, malformed, and out-of-range input in separate stages.
 ```python
-choice = "9"
-match choice:
-    case "1":
-        print("Balance")
-    case "2":
-        print("Deposit")
-print("Menu closed")
-```
-What does the program print?</x:v>
+raw = input("Age: ")
+if not raw:
+    result = "Required"
+elif __________:
+    result = "Digits only"
+else:
+    age = int(raw)
+    result = "Accepted" if 1 &lt;= age &lt;= 120 else "Out of range"
+```</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Neither named case matches `"9"`, and there is no `case _`, so the `match` block prints nothing. Execution then continues after the block and prints `Menu closed`.</x:v>
+        <x:v>The second guard rejects malformed non-empty text before execution can reach `int(raw)`.</x:v>
       </x:c>
       <x:c r="D38" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E38" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>python - Set 2</x:v>
@@ -2653,60 +2595,50 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>match-case</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>Menu closed only</x:v>
+        <x:v>`raw.isdigit()`</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Balance, then Menu closed</x:v>
+        <x:v>`not raw.isdigit()`</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>An error because case _ is required</x:v>
+        <x:v>`int(raw) &gt; 120`</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Nothing</x:v>
+        <x:v>`raw == True`</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>Python - MCQ - 3.2.28</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A checked-in passenger arrives with 2 bags. The free allowance is up to 2 bags:
+        <x:v>A checkout team is documenting exactly how Python groups a combined member-and-coupon rule.
 ```python
-checked_in = True
-bags = 2
-if checked_in:
-    if bags == 0:
-        print("No baggage")
-    elif bags &lt;= 2:
-        print("Within free allowance")
-    else:
-        print("Excess baggage fee")
-else:
-    print("Please check in first")
+member and total &gt;= 500 or coupon == "SAVE"
 ```
-Which message shows?</x:v>
+Choose the fully parenthesised equivalent.</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>The passenger is checked in, so the inner chain runs. `bags == 0` is False, then `bags &lt;= 2` is `2 &lt;= 2` → True, so it prints `Within free allowance`. The inner `else` and the outer `else` are both skipped.</x:v>
+        <x:v>Comparisons are evaluated before Boolean operators, and `and` binds more tightly than `or`.</x:v>
       </x:c>
       <x:c r="D39" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E39" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>python - Set 2</x:v>
@@ -2718,58 +2650,53 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>nested-conditions-and-guard-clauses</x:v>
+        <x:v>truthiness-and-boolean-logic</x:v>
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>Within free allowance</x:v>
+        <x:v>`member and (total &gt;= 500 or coupon == "SAVE")`</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Excess baggage fee</x:v>
+        <x:v>`(member and total) &gt;= (500 or coupon == "SAVE")`</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>No baggage</x:v>
+        <x:v>`member and total &gt;= (500 or coupon) == "SAVE"`</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Please check in first</x:v>
+        <x:v>`(member and total &gt;= 500) or (coupon == "SAVE")`</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>Python - MCQ - 3.2.29</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>A registration form first checks whether an age entry contains only digits. It converts the entry only after that check succeeds:
+        <x:v>A clinic program must always confirm that a temperature check finished, whether or not fever is detected.
 ```python
-entry = input("Age: ")
-if entry.isdigit():
-    age = int(entry)
-    if age &gt;= 18:
-        print("Accepted")
-    else:
-        print("Must be 18 or older")
-else:
-    print("Digits only")
+temperature = 37
+if temperature &gt;= 38:
+    print("Fever")
+print("Check complete")
 ```
-Which flat rewrite preserves all three outcomes without trying `int(entry)` on invalid text?</x:v>
+Complete the statement: `"Check complete"` executes _____ because it is _____.</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>The safe order is: reject non-digits first, convert only in the remaining branches, then separate adults from under-18 entries. Option C does exactly that. The other rewrites either convert invalid text too early, accept every digit-only entry without checking the age, or attach the final message to the wrong condition.</x:v>
+        <x:v>The line is not indented, so it lies after the decision and runs regardless of the condition.</x:v>
       </x:c>
       <x:c r="D40" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E40" t="str">
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>analyze</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>python - Set 2</x:v>
@@ -2781,51 +2708,35 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>input-validation</x:v>
+        <x:v>conditional-statements</x:v>
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>`if int(entry) &gt;= 18: print("Accepted")`
-`elif not entry.isdigit(): print("Digits only")`
-`else: print("Must be 18 or older")`</x:v>
+        <x:v>always; outside the indented `if` block</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>`if not entry.isdigit(): print("Digits only")`
-`elif int(entry) &lt; 18: print("Must be 18 or older")`
-`else: print("Accepted")`</x:v>
+        <x:v>never; below an `if` statement</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>`if entry.isdigit(): print("Accepted")`
-`elif int(entry) &lt; 18: print("Must be 18 or older")`
-`else: print("Digits only")`</x:v>
+        <x:v>only for fever; part of the indented block</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>`if not entry.isdigit(): print("Digits only")`
-`elif int(entry) &gt;= 18: print("Must be 18 or older")`
-`else: print("Accepted")`</x:v>
+        <x:v>only when the condition is false; an implicit `else`</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>Python - MCQ - 3.2.30</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>A signup button lights only when both the name and email are filled. The name is "Ravi", but the email box was left empty:
-```python
-name = "Ravi"
-email = ""
-if name and email:
-    print("Form ready")
-else:
-    print("Complete all fields")
-```
-What does the check decide?</x:v>
+        <x:v>An exam form needs a complete one-shot validation flow for missing, malformed, and excessive marks.
+A one-shot exam form must report missing input, reject non-digits without crashing, reject marks above 100, and accept valid marks. Choose the complete pipeline.</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>`name` is a non-empty (truthy) string, but `email` is `""`, which is falsy. `and` needs both sides truthy, so `"Ravi" and ""` is False overall and the `else` runs, printing `Complete all fields`. One empty field is enough to fail the check.</x:v>
+        <x:v>Empty and malformed inputs are rejected before conversion; only safe numeric text reaches the range check.</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>8</x:v>
@@ -2849,23 +2760,45 @@
         <x:v>control-flow</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>truthiness-and-boolean-logic</x:v>
+        <x:v>input-validation</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>Form ready — the name is filled, that is enough</x:v>
+        <x:v>```python
+mark = int(raw)
+if mark &lt;= 100:
+    result = "Accepted"
+```</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>An error — you cannot use and with strings</x:v>
+        <x:v>```python
+if raw or raw.isdigit():
+    result = "Accepted"
+else:
+    result = "Rejected"
+```</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Form ready — a filled name makes the whole thing true</x:v>
+        <x:v>```python
+if not raw:
+    result = "Required"
+elif not raw.isdigit():
+    result = "Digits only"
+else:
+    mark = int(raw)
+    result = "Accepted" if mark &lt;= 100 else "Out of range"
+```</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Complete all fields — the empty email is falsy, so the and is False</x:v>
+        <x:v>```python
+if not raw and int(raw) &gt; 100:
+    result = "Rejected"
+else:
+    result = "Accepted"
+```</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
